--- a/E/EG3A.xlsx
+++ b/E/EG3A.xlsx
@@ -73,7 +73,7 @@
     <t>10006260</t>
   </si>
   <si>
-    <t>DNCOW FRTGO COK 780</t>
+    <t>DNCOW FRGO CKT 780 G</t>
   </si>
   <si>
     <t>20027848</t>

--- a/E/EG3A.xlsx
+++ b/E/EG3A.xlsx
@@ -11,186 +11,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
+    <t>20072925</t>
+  </si>
+  <si>
+    <t>BABY HAPY PANTS 28/L</t>
+  </si>
+  <si>
+    <t>EG3A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20072924</t>
+  </si>
+  <si>
+    <t>BABY HAPY PANTS26/XL</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20045423</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL26</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20073638</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE M/32'S</t>
+  </si>
+  <si>
     <t>20070712</t>
   </si>
   <si>
     <t>MERRIES PANT GS28 L</t>
   </si>
   <si>
-    <t>EG3A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20095875</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 28'S L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW1+ VAN BX 750 G</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRGO CKT 780 G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW1+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW3+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MD 900 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20020120</t>
-  </si>
-  <si>
-    <t>CUSSON H&amp;BW ML&amp;G 375</t>
-  </si>
-  <si>
-    <t>20135778</t>
-  </si>
-  <si>
-    <t>CSSONS H&amp;B DP.MST375</t>
-  </si>
-  <si>
-    <t>20134049</t>
-  </si>
-  <si>
-    <t>KODOMO BB H&amp;B ALO400</t>
-  </si>
-  <si>
-    <t>20002133</t>
-  </si>
-  <si>
-    <t>IDM CT.BUD BABY R100</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20115786</t>
-  </si>
-  <si>
-    <t>IDM CTN.BUDS RFL 100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20052548</t>
-  </si>
-  <si>
-    <t>KONICARE TLN PLS 125</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20064412</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL ASLI 270</t>
+    <t>20087019</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU 1000 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20063027</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT.PDS 270</t>
-  </si>
-  <si>
-    <t>20029222</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BEEF50</t>
-  </si>
-  <si>
-    <t>20141207</t>
-  </si>
-  <si>
-    <t>WATERU WHT BMBOO 50S</t>
-  </si>
-  <si>
-    <t>20138469</t>
-  </si>
-  <si>
-    <t>SNSODYNE CGH GB</t>
-  </si>
-  <si>
-    <t>20134770</t>
-  </si>
-  <si>
-    <t>DOVE R/ON SRM+CLG 50</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10027167</t>
-  </si>
-  <si>
-    <t>DOVE DEO CMP.CARE 40</t>
+    <t>20069147</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VN BX 1 KG</t>
+  </si>
+  <si>
+    <t>20142953</t>
+  </si>
+  <si>
+    <t>BEBELAC 3+ VAN 775 G</t>
+  </si>
+  <si>
+    <t>20142952</t>
+  </si>
+  <si>
+    <t>BEBELAC 3+ MDU 775 G</t>
   </si>
 </sst>
 </file>
@@ -583,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -650,15 +584,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -667,18 +601,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -690,15 +624,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -710,27 +644,27 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,73 +678,73 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -824,13 +758,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,193 +778,33 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG3A.xlsx
+++ b/E/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t/>
   </si>
@@ -67,64 +67,67 @@
     <t>RT</t>
   </si>
   <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW1+ VAN BX 750 G</t>
+    <t>20142951</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ MADU 775</t>
+  </si>
+  <si>
+    <t>20122288</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ V BX 600 G</t>
+  </si>
+  <si>
+    <t>20122291</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ M BX 600 G</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW3+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW1+ MDU BX 750 G</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW3+ MDU BX 750 G</t>
-  </si>
-  <si>
-    <t>20066494</t>
-  </si>
-  <si>
-    <t>SGM EKSPL5+ MD 900 G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20087019</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ MDU 1000 G</t>
+    <t>10015650</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BX 750 G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRGO CKT 780 G</t>
+  </si>
+  <si>
+    <t>20069146</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MD BX 1 KG</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MD 600 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20069147</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VN BX 1 KG</t>
-  </si>
-  <si>
-    <t>20142953</t>
-  </si>
-  <si>
-    <t>BEBELAC 3+ VAN 775 G</t>
-  </si>
-  <si>
-    <t>20142952</t>
-  </si>
-  <si>
-    <t>BEBELAC 3+ MDU 775 G</t>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VN 600 G</t>
   </si>
 </sst>
 </file>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -664,15 +667,15 @@
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -684,15 +687,15 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -704,107 +707,127 @@
         <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
